--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N24_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N24_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>14.41626041559763</v>
+        <v>2.342642317534615</v>
       </c>
       <c r="D2" t="n">
-        <v>23.91909781113547</v>
+        <v>3.886853394309514</v>
       </c>
       <c r="E2" t="n">
-        <v>13.82188279076456</v>
+        <v>2.246055953499241</v>
       </c>
       <c r="F2" t="n">
-        <v>11.87519111275922</v>
+        <v>1.929718555823373</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.64784085871688</v>
+        <v>4.330274139541493</v>
       </c>
       <c r="D3" t="n">
-        <v>35.22349181657039</v>
+        <v>5.723817420192689</v>
       </c>
       <c r="E3" t="n">
-        <v>13.82188279076456</v>
+        <v>2.246055953499241</v>
       </c>
       <c r="F3" t="n">
-        <v>11.87519111275922</v>
+        <v>1.929718555823373</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>33.54520065054062</v>
+        <v>5.451095105712851</v>
       </c>
       <c r="D4" t="n">
-        <v>41.41515637142865</v>
+        <v>6.729962910357156</v>
       </c>
       <c r="E4" t="n">
-        <v>13.82188279076456</v>
+        <v>2.246055953499241</v>
       </c>
       <c r="F4" t="n">
-        <v>11.87519111275922</v>
+        <v>1.929718555823373</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>54.96501382945268</v>
+        <v>8.931814747286062</v>
       </c>
       <c r="D5" t="n">
-        <v>44.90529509315542</v>
+        <v>7.297110452637756</v>
       </c>
       <c r="E5" t="n">
-        <v>13.82188279076456</v>
+        <v>2.246055953499241</v>
       </c>
       <c r="F5" t="n">
-        <v>11.87519111275922</v>
+        <v>1.929718555823373</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>16.00978406697157</v>
+        <v>2.601589910882879</v>
       </c>
       <c r="D6" t="n">
-        <v>46.51613708798583</v>
+        <v>7.558872276797698</v>
       </c>
       <c r="E6" t="n">
-        <v>13.82188279076456</v>
+        <v>2.246055953499241</v>
       </c>
       <c r="F6" t="n">
-        <v>11.87519111275922</v>
+        <v>1.929718555823373</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>26.2020932353283</v>
+        <v>4.257840150740849</v>
       </c>
       <c r="D7" t="n">
-        <v>26.84503532082955</v>
+        <v>4.362318239634802</v>
       </c>
       <c r="E7" t="n">
-        <v>13.82188279076456</v>
+        <v>2.246055953499241</v>
       </c>
       <c r="F7" t="n">
-        <v>11.87519111275922</v>
+        <v>1.929718555823373</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>36.70194430884258</v>
+        <v>5.96406595018692</v>
       </c>
       <c r="D8" t="n">
-        <v>55.60197519217316</v>
+        <v>9.035320968728138</v>
       </c>
       <c r="E8" t="n">
-        <v>13.82188279076456</v>
+        <v>2.246055953499241</v>
       </c>
       <c r="F8" t="n">
-        <v>11.87519111275922</v>
+        <v>1.929718555823373</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>50.7249028100549</v>
+        <v>8.242796706633921</v>
       </c>
       <c r="D9" t="n">
-        <v>18.74640706316221</v>
+        <v>3.046291147763859</v>
       </c>
       <c r="E9" t="n">
-        <v>13.82188279076456</v>
+        <v>2.246055953499241</v>
       </c>
       <c r="F9" t="n">
-        <v>11.87519111275922</v>
+        <v>1.929718555823373</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
